--- a/Versão5/ABNT/Ontologia_15965_5I.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_5I.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D955C7E-47BC-4A8A-85C1-D93ADB0D6E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -5619,23 +5619,13 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{8576210E-162F-453B-B886-CD2163C7562E}"/>
   </cellStyles>
-  <dxfs count="22">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="21">
     <dxf>
       <font>
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color theme="0"/>
       </font>
     </dxf>
     <dxf>
@@ -5723,7 +5713,7 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -6145,14 +6135,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FFEA285-1F1C-49D4-8690-0B8CB6A5C474}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="8.65" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.69921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>4</v>
       </c>
@@ -6163,7 +6153,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>19</v>
       </c>
@@ -6174,7 +6164,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>20</v>
       </c>
@@ -6185,7 +6175,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>5</v>
       </c>
@@ -6196,7 +6186,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>6</v>
       </c>
@@ -6208,7 +6198,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>7</v>
       </c>
@@ -6220,7 +6210,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>8</v>
       </c>
@@ -6231,7 +6221,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>9</v>
       </c>
@@ -6242,7 +6232,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>21</v>
       </c>
@@ -6253,7 +6243,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>23</v>
       </c>
@@ -6264,7 +6254,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>24</v>
       </c>
@@ -6275,7 +6265,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>10</v>
       </c>
@@ -6286,7 +6276,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>25</v>
       </c>
@@ -6297,7 +6287,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>26</v>
       </c>
@@ -6308,7 +6298,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>27</v>
       </c>
@@ -6319,7 +6309,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>28</v>
       </c>
@@ -6330,7 +6320,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>12</v>
       </c>
@@ -6341,19 +6331,19 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>29</v>
       </c>
       <c r="B18" s="4">
         <f ca="1">NOW()</f>
-        <v>46148.617392476852</v>
+        <v>46157.682782754629</v>
       </c>
       <c r="C18" s="45" t="s">
         <v>1545</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>1553</v>
       </c>
@@ -6364,7 +6354,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>1549</v>
       </c>
@@ -6376,7 +6366,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>1554</v>
       </c>
@@ -6388,7 +6378,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>18</v>
       </c>
@@ -6399,7 +6389,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>30</v>
       </c>
@@ -6410,7 +6400,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>34</v>
       </c>
@@ -6421,7 +6411,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>35</v>
       </c>
@@ -6432,7 +6422,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="46" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" s="46" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>1542</v>
       </c>
@@ -6452,34 +6442,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1A90C8D-F4F0-474F-8F2D-D62CBC6EB14C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA19"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" style="33" customWidth="1"/>
+    <col min="1" max="1" width="2.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.796875" style="33" customWidth="1"/>
     <col min="3" max="3" width="6.5" style="33" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.83203125" style="33" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.33203125" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.796875" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.296875" style="33" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="33" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.6640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.69921875" style="33" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="75.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="75.796875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="56.5" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7" customWidth="1"/>
-    <col min="20" max="20" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.296875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="9" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="6" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="79.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="79.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="57.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="30.9" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>1483</v>
       </c>
@@ -6562,7 +6552,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="57">
         <v>2</v>
       </c>
@@ -6653,7 +6643,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="57">
         <v>3</v>
       </c>
@@ -6744,7 +6734,7 @@
         <v>1567</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="57">
         <v>4</v>
       </c>
@@ -6835,7 +6825,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="57">
         <v>5</v>
       </c>
@@ -6926,7 +6916,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="57">
         <v>6</v>
       </c>
@@ -7017,7 +7007,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="57">
         <v>7</v>
       </c>
@@ -7108,7 +7098,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="57">
         <v>8</v>
       </c>
@@ -7199,7 +7189,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="57">
         <v>9</v>
       </c>
@@ -7290,7 +7280,7 @@
         <v>1591</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="57">
         <v>10</v>
       </c>
@@ -7381,7 +7371,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="57">
         <v>11</v>
       </c>
@@ -7472,7 +7462,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="57">
         <v>12</v>
       </c>
@@ -7563,7 +7553,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="57">
         <v>13</v>
       </c>
@@ -7654,7 +7644,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="57">
         <v>14</v>
       </c>
@@ -7745,7 +7735,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="57">
         <v>15</v>
       </c>
@@ -7836,7 +7826,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="57">
         <v>16</v>
       </c>
@@ -7927,7 +7917,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="57">
         <v>17</v>
       </c>
@@ -8018,7 +8008,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="57">
         <v>18</v>
       </c>
@@ -8109,7 +8099,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="57">
         <v>19</v>
       </c>
@@ -8202,18 +8192,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A19">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="20" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA1:AA19">
-    <cfRule type="cellIs" dxfId="16" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8228,13 +8218,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1AA270-C700-44D7-AFAB-8480CF5F2B6E}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
       <c r="A1" s="27" t="s">
         <v>1484</v>
       </c>
@@ -8299,7 +8289,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="27">
         <v>2</v>
       </c>
@@ -8366,7 +8356,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8381,14 +8371,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCBE7ADA-121D-48D5-88A4-2E192550983E}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.69921875" customWidth="1"/>
+    <col min="3" max="3" width="16.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="30">
         <v>1</v>
       </c>
@@ -8399,7 +8389,7 @@
         <v>1532</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -8412,7 +8402,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8424,39 +8414,39 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AA732"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.19921875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.296875" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.83203125" style="9" customWidth="1"/>
-    <col min="9" max="9" width="6.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.83203125" style="9" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.796875" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.796875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="16.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.296875" style="9" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="23.5" style="9" customWidth="1"/>
     <col min="14" max="14" width="6" style="9" customWidth="1"/>
-    <col min="15" max="15" width="45.6640625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9.6640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="45.69921875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9.69921875" style="1" customWidth="1"/>
     <col min="17" max="17" width="29" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.83203125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="22.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.83203125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="14.6640625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="8.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.796875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="22.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.796875" style="1" customWidth="1"/>
+    <col min="25" max="25" width="14.69921875" style="1" customWidth="1"/>
     <col min="26" max="26" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.1640625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="11.19921875" style="1" customWidth="1"/>
     <col min="28" max="16384" width="11.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>31</v>
       </c>
@@ -8539,7 +8529,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12">
         <v>2</v>
       </c>
@@ -8622,7 +8612,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12">
         <v>3</v>
       </c>
@@ -8705,7 +8695,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12">
         <v>4</v>
       </c>
@@ -8788,7 +8778,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>5</v>
       </c>
@@ -8871,7 +8861,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>6</v>
       </c>
@@ -8954,7 +8944,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>7</v>
       </c>
@@ -9037,7 +9027,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>8</v>
       </c>
@@ -9120,7 +9110,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>9</v>
       </c>
@@ -9203,7 +9193,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>10</v>
       </c>
@@ -9286,7 +9276,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12">
         <v>11</v>
       </c>
@@ -9369,7 +9359,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12">
         <v>12</v>
       </c>
@@ -9452,7 +9442,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12">
         <v>13</v>
       </c>
@@ -9535,7 +9525,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12">
         <v>14</v>
       </c>
@@ -9618,7 +9608,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12">
         <v>15</v>
       </c>
@@ -9701,7 +9691,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12">
         <v>16</v>
       </c>
@@ -9784,7 +9774,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12">
         <v>17</v>
       </c>
@@ -9867,7 +9857,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12">
         <v>18</v>
       </c>
@@ -9950,7 +9940,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12">
         <v>19</v>
       </c>
@@ -10033,7 +10023,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12">
         <v>20</v>
       </c>
@@ -10116,7 +10106,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12">
         <v>21</v>
       </c>
@@ -10199,7 +10189,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12">
         <v>22</v>
       </c>
@@ -10282,7 +10272,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12">
         <v>23</v>
       </c>
@@ -10365,7 +10355,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12">
         <v>24</v>
       </c>
@@ -10448,7 +10438,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12">
         <v>25</v>
       </c>
@@ -10531,7 +10521,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12">
         <v>26</v>
       </c>
@@ -10614,7 +10604,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12">
         <v>27</v>
       </c>
@@ -10697,7 +10687,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12">
         <v>28</v>
       </c>
@@ -10780,7 +10770,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12">
         <v>29</v>
       </c>
@@ -10863,7 +10853,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12">
         <v>30</v>
       </c>
@@ -10946,7 +10936,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12">
         <v>31</v>
       </c>
@@ -11029,7 +11019,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12">
         <v>32</v>
       </c>
@@ -11112,7 +11102,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12">
         <v>33</v>
       </c>
@@ -11195,7 +11185,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12">
         <v>34</v>
       </c>
@@ -11278,7 +11268,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12">
         <v>35</v>
       </c>
@@ -11361,7 +11351,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12">
         <v>36</v>
       </c>
@@ -11444,7 +11434,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12">
         <v>37</v>
       </c>
@@ -11527,7 +11517,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12">
         <v>38</v>
       </c>
@@ -11610,7 +11600,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12">
         <v>39</v>
       </c>
@@ -11693,7 +11683,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12">
         <v>40</v>
       </c>
@@ -11776,7 +11766,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12">
         <v>41</v>
       </c>
@@ -11859,7 +11849,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12">
         <v>42</v>
       </c>
@@ -11942,7 +11932,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12">
         <v>43</v>
       </c>
@@ -12025,7 +12015,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="12">
         <v>44</v>
       </c>
@@ -12108,7 +12098,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12">
         <v>45</v>
       </c>
@@ -12191,7 +12181,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="12">
         <v>46</v>
       </c>
@@ -12274,7 +12264,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12">
         <v>47</v>
       </c>
@@ -12357,7 +12347,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12">
         <v>48</v>
       </c>
@@ -12440,7 +12430,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12">
         <v>49</v>
       </c>
@@ -12523,7 +12513,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="12">
         <v>50</v>
       </c>
@@ -12606,7 +12596,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="12">
         <v>51</v>
       </c>
@@ -12689,7 +12679,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="12">
         <v>52</v>
       </c>
@@ -12772,7 +12762,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="12">
         <v>53</v>
       </c>
@@ -12855,7 +12845,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="12">
         <v>54</v>
       </c>
@@ -12938,7 +12928,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="12">
         <v>55</v>
       </c>
@@ -13021,7 +13011,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="12">
         <v>56</v>
       </c>
@@ -13104,7 +13094,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="12">
         <v>57</v>
       </c>
@@ -13187,7 +13177,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="12">
         <v>58</v>
       </c>
@@ -13270,7 +13260,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="12">
         <v>59</v>
       </c>
@@ -13353,7 +13343,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="12">
         <v>60</v>
       </c>
@@ -13436,7 +13426,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="12">
         <v>61</v>
       </c>
@@ -13519,7 +13509,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12">
         <v>62</v>
       </c>
@@ -13602,7 +13592,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="12">
         <v>63</v>
       </c>
@@ -13685,7 +13675,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="12">
         <v>64</v>
       </c>
@@ -13768,7 +13758,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="12">
         <v>65</v>
       </c>
@@ -13851,7 +13841,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="12">
         <v>66</v>
       </c>
@@ -13934,7 +13924,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="12">
         <v>67</v>
       </c>
@@ -14017,7 +14007,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="12">
         <v>68</v>
       </c>
@@ -14100,7 +14090,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="12">
         <v>69</v>
       </c>
@@ -14183,7 +14173,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="12">
         <v>70</v>
       </c>
@@ -14266,7 +14256,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="12">
         <v>71</v>
       </c>
@@ -14349,7 +14339,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12">
         <v>72</v>
       </c>
@@ -14432,7 +14422,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="12">
         <v>73</v>
       </c>
@@ -14515,7 +14505,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="12">
         <v>74</v>
       </c>
@@ -14598,7 +14588,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="12">
         <v>75</v>
       </c>
@@ -14681,7 +14671,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="12">
         <v>76</v>
       </c>
@@ -14764,7 +14754,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="12">
         <v>77</v>
       </c>
@@ -14847,7 +14837,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="12">
         <v>78</v>
       </c>
@@ -14930,7 +14920,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="12">
         <v>79</v>
       </c>
@@ -15013,7 +15003,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="12">
         <v>80</v>
       </c>
@@ -15096,7 +15086,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12">
         <v>81</v>
       </c>
@@ -15179,7 +15169,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12">
         <v>82</v>
       </c>
@@ -15262,7 +15252,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="12">
         <v>83</v>
       </c>
@@ -15345,7 +15335,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12">
         <v>84</v>
       </c>
@@ -15428,7 +15418,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="12">
         <v>85</v>
       </c>
@@ -15511,7 +15501,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="12">
         <v>86</v>
       </c>
@@ -15594,7 +15584,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="12">
         <v>87</v>
       </c>
@@ -15677,7 +15667,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="12">
         <v>88</v>
       </c>
@@ -15760,7 +15750,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="12">
         <v>89</v>
       </c>
@@ -15843,7 +15833,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12">
         <v>90</v>
       </c>
@@ -15926,7 +15916,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="12">
         <v>91</v>
       </c>
@@ -16009,7 +15999,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="12">
         <v>92</v>
       </c>
@@ -16092,7 +16082,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="12">
         <v>93</v>
       </c>
@@ -16175,7 +16165,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="12">
         <v>94</v>
       </c>
@@ -16258,7 +16248,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="12">
         <v>95</v>
       </c>
@@ -16341,7 +16331,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12">
         <v>96</v>
       </c>
@@ -16424,7 +16414,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="12">
         <v>97</v>
       </c>
@@ -16507,7 +16497,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="12">
         <v>98</v>
       </c>
@@ -16590,7 +16580,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="12">
         <v>99</v>
       </c>
@@ -16673,7 +16663,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12">
         <v>100</v>
       </c>
@@ -16756,7 +16746,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="12">
         <v>101</v>
       </c>
@@ -16839,7 +16829,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="102" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12">
         <v>102</v>
       </c>
@@ -16922,7 +16912,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="103" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="12">
         <v>103</v>
       </c>
@@ -17005,7 +16995,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="12">
         <v>104</v>
       </c>
@@ -17088,7 +17078,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="12">
         <v>105</v>
       </c>
@@ -17171,7 +17161,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="12">
         <v>106</v>
       </c>
@@ -17254,7 +17244,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="12">
         <v>107</v>
       </c>
@@ -17337,7 +17327,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="12">
         <v>108</v>
       </c>
@@ -17420,7 +17410,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="12">
         <v>109</v>
       </c>
@@ -17503,7 +17493,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="12">
         <v>110</v>
       </c>
@@ -17586,7 +17576,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="12">
         <v>111</v>
       </c>
@@ -17669,7 +17659,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="12">
         <v>112</v>
       </c>
@@ -17752,7 +17742,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="12">
         <v>113</v>
       </c>
@@ -17835,7 +17825,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="12">
         <v>114</v>
       </c>
@@ -17918,7 +17908,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="12">
         <v>115</v>
       </c>
@@ -18001,7 +17991,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="12">
         <v>116</v>
       </c>
@@ -18084,7 +18074,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="12">
         <v>117</v>
       </c>
@@ -18167,7 +18157,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="12">
         <v>118</v>
       </c>
@@ -18250,7 +18240,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="12">
         <v>119</v>
       </c>
@@ -18333,7 +18323,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="12">
         <v>120</v>
       </c>
@@ -18416,7 +18406,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="12">
         <v>121</v>
       </c>
@@ -18499,7 +18489,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="12">
         <v>122</v>
       </c>
@@ -18582,7 +18572,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="12">
         <v>123</v>
       </c>
@@ -18665,7 +18655,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="12">
         <v>124</v>
       </c>
@@ -18748,7 +18738,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="12">
         <v>125</v>
       </c>
@@ -18831,7 +18821,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="12">
         <v>126</v>
       </c>
@@ -18914,7 +18904,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="12">
         <v>127</v>
       </c>
@@ -18997,7 +18987,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="128" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="12">
         <v>128</v>
       </c>
@@ -19080,7 +19070,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="129" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="12">
         <v>129</v>
       </c>
@@ -19163,7 +19153,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="130" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="12">
         <v>130</v>
       </c>
@@ -19246,7 +19236,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="131" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="12">
         <v>131</v>
       </c>
@@ -19329,7 +19319,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="132" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="12">
         <v>132</v>
       </c>
@@ -19412,7 +19402,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="133" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="12">
         <v>133</v>
       </c>
@@ -19495,7 +19485,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="134" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="12">
         <v>134</v>
       </c>
@@ -19578,7 +19568,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="135" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="12">
         <v>135</v>
       </c>
@@ -19661,7 +19651,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="136" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="12">
         <v>136</v>
       </c>
@@ -19744,7 +19734,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="137" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="12">
         <v>137</v>
       </c>
@@ -19827,7 +19817,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="138" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="12">
         <v>138</v>
       </c>
@@ -19910,7 +19900,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="139" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="12">
         <v>139</v>
       </c>
@@ -19993,7 +19983,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="140" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="12">
         <v>140</v>
       </c>
@@ -20076,7 +20066,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="141" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="12">
         <v>141</v>
       </c>
@@ -20159,7 +20149,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="142" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="12">
         <v>142</v>
       </c>
@@ -20242,7 +20232,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="143" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="12">
         <v>143</v>
       </c>
@@ -20325,7 +20315,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="144" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="12">
         <v>144</v>
       </c>
@@ -20408,7 +20398,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="145" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="12">
         <v>145</v>
       </c>
@@ -20491,7 +20481,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="146" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="12">
         <v>146</v>
       </c>
@@ -20574,7 +20564,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="147" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="12">
         <v>147</v>
       </c>
@@ -20657,7 +20647,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="148" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="12">
         <v>148</v>
       </c>
@@ -20740,7 +20730,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="149" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="12">
         <v>149</v>
       </c>
@@ -20823,7 +20813,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="150" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="12">
         <v>150</v>
       </c>
@@ -20906,7 +20896,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="151" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="12">
         <v>151</v>
       </c>
@@ -20989,7 +20979,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="152" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="12">
         <v>152</v>
       </c>
@@ -21072,7 +21062,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="153" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="12">
         <v>153</v>
       </c>
@@ -21155,7 +21145,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="154" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="12">
         <v>154</v>
       </c>
@@ -21238,7 +21228,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="155" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="12">
         <v>155</v>
       </c>
@@ -21321,7 +21311,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="156" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="12">
         <v>156</v>
       </c>
@@ -21404,7 +21394,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="157" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="12">
         <v>157</v>
       </c>
@@ -21487,7 +21477,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="158" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="12">
         <v>158</v>
       </c>
@@ -21570,7 +21560,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="159" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="12">
         <v>159</v>
       </c>
@@ -21653,7 +21643,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="160" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="12">
         <v>160</v>
       </c>
@@ -21736,7 +21726,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="161" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="12">
         <v>161</v>
       </c>
@@ -21819,7 +21809,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="162" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="12">
         <v>162</v>
       </c>
@@ -21902,7 +21892,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="163" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="12">
         <v>163</v>
       </c>
@@ -21985,7 +21975,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="164" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="12">
         <v>164</v>
       </c>
@@ -22068,7 +22058,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="165" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="12">
         <v>165</v>
       </c>
@@ -22151,7 +22141,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="166" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="12">
         <v>166</v>
       </c>
@@ -22234,7 +22224,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="167" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="12">
         <v>167</v>
       </c>
@@ -22317,7 +22307,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="168" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="12">
         <v>168</v>
       </c>
@@ -22400,7 +22390,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="169" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="12">
         <v>169</v>
       </c>
@@ -22483,7 +22473,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="170" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="12">
         <v>170</v>
       </c>
@@ -22566,7 +22556,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="171" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="12">
         <v>171</v>
       </c>
@@ -22649,7 +22639,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="172" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="12">
         <v>172</v>
       </c>
@@ -22732,7 +22722,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="173" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="12">
         <v>173</v>
       </c>
@@ -22815,7 +22805,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="174" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="12">
         <v>174</v>
       </c>
@@ -22898,7 +22888,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="175" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="12">
         <v>175</v>
       </c>
@@ -22981,7 +22971,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="176" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="12">
         <v>176</v>
       </c>
@@ -23064,7 +23054,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="177" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="12">
         <v>177</v>
       </c>
@@ -23147,7 +23137,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="178" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="12">
         <v>178</v>
       </c>
@@ -23230,7 +23220,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="179" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="12">
         <v>179</v>
       </c>
@@ -23313,7 +23303,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="180" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="12">
         <v>180</v>
       </c>
@@ -23396,7 +23386,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="181" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="12">
         <v>181</v>
       </c>
@@ -23479,7 +23469,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="182" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="12">
         <v>182</v>
       </c>
@@ -23562,7 +23552,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="183" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="12">
         <v>183</v>
       </c>
@@ -23645,7 +23635,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="184" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="12">
         <v>184</v>
       </c>
@@ -23728,7 +23718,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="185" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="12">
         <v>185</v>
       </c>
@@ -23811,7 +23801,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="186" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="12">
         <v>186</v>
       </c>
@@ -23894,7 +23884,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="187" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="12">
         <v>187</v>
       </c>
@@ -23977,7 +23967,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="188" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="12">
         <v>188</v>
       </c>
@@ -24060,7 +24050,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="189" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="12">
         <v>189</v>
       </c>
@@ -24143,7 +24133,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="190" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="12">
         <v>190</v>
       </c>
@@ -24226,7 +24216,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="191" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="12">
         <v>191</v>
       </c>
@@ -24309,7 +24299,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="192" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="12">
         <v>192</v>
       </c>
@@ -24392,7 +24382,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="193" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="12">
         <v>193</v>
       </c>
@@ -24475,7 +24465,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="194" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="12">
         <v>194</v>
       </c>
@@ -24558,7 +24548,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="195" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="12">
         <v>195</v>
       </c>
@@ -24641,7 +24631,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="196" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="12">
         <v>196</v>
       </c>
@@ -24724,7 +24714,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="197" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="12">
         <v>197</v>
       </c>
@@ -24807,7 +24797,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="198" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="12">
         <v>198</v>
       </c>
@@ -24890,7 +24880,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="199" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="12">
         <v>199</v>
       </c>
@@ -24973,7 +24963,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="200" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="12">
         <v>200</v>
       </c>
@@ -25056,7 +25046,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="201" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="12">
         <v>201</v>
       </c>
@@ -25139,7 +25129,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="202" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="12">
         <v>202</v>
       </c>
@@ -25222,7 +25212,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="203" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="12">
         <v>203</v>
       </c>
@@ -25305,7 +25295,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="204" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="12">
         <v>204</v>
       </c>
@@ -25388,7 +25378,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="205" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="12">
         <v>205</v>
       </c>
@@ -25471,7 +25461,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="206" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="12">
         <v>206</v>
       </c>
@@ -25554,7 +25544,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="207" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="12">
         <v>207</v>
       </c>
@@ -25637,7 +25627,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="208" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="12">
         <v>208</v>
       </c>
@@ -25720,7 +25710,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="209" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="12">
         <v>209</v>
       </c>
@@ -25803,7 +25793,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="210" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="12">
         <v>210</v>
       </c>
@@ -25886,7 +25876,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="211" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="12">
         <v>211</v>
       </c>
@@ -25969,7 +25959,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="212" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="12">
         <v>212</v>
       </c>
@@ -26052,7 +26042,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="213" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="12">
         <v>213</v>
       </c>
@@ -26135,7 +26125,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="214" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="12">
         <v>214</v>
       </c>
@@ -26218,7 +26208,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="215" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="12">
         <v>215</v>
       </c>
@@ -26301,7 +26291,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="216" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="12">
         <v>216</v>
       </c>
@@ -26384,7 +26374,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="217" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="12">
         <v>217</v>
       </c>
@@ -26467,7 +26457,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="218" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="12">
         <v>218</v>
       </c>
@@ -26550,7 +26540,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="219" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="12">
         <v>219</v>
       </c>
@@ -26633,7 +26623,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="220" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="12">
         <v>220</v>
       </c>
@@ -26716,7 +26706,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="221" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="12">
         <v>221</v>
       </c>
@@ -26799,7 +26789,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="222" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="12">
         <v>222</v>
       </c>
@@ -26882,7 +26872,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="223" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="12">
         <v>223</v>
       </c>
@@ -26965,7 +26955,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="224" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="12">
         <v>224</v>
       </c>
@@ -27048,7 +27038,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="225" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="12">
         <v>225</v>
       </c>
@@ -27131,7 +27121,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="226" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="12">
         <v>226</v>
       </c>
@@ -27214,7 +27204,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="227" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="12">
         <v>227</v>
       </c>
@@ -27297,7 +27287,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="228" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="12">
         <v>228</v>
       </c>
@@ -27380,7 +27370,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="229" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="12">
         <v>229</v>
       </c>
@@ -27463,7 +27453,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="230" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="12">
         <v>230</v>
       </c>
@@ -27546,7 +27536,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="231" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="12">
         <v>231</v>
       </c>
@@ -27629,7 +27619,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="232" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="12">
         <v>232</v>
       </c>
@@ -27712,7 +27702,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="233" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="12">
         <v>233</v>
       </c>
@@ -27795,7 +27785,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="234" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="12">
         <v>234</v>
       </c>
@@ -27878,7 +27868,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="235" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="12">
         <v>235</v>
       </c>
@@ -27961,7 +27951,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="236" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="12">
         <v>236</v>
       </c>
@@ -28044,7 +28034,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="237" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="12">
         <v>237</v>
       </c>
@@ -28127,7 +28117,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="238" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="12">
         <v>238</v>
       </c>
@@ -28210,7 +28200,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="239" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="12">
         <v>239</v>
       </c>
@@ -28293,7 +28283,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="240" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="12">
         <v>240</v>
       </c>
@@ -28376,7 +28366,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="241" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="12">
         <v>241</v>
       </c>
@@ -28459,7 +28449,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="242" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="12">
         <v>242</v>
       </c>
@@ -28542,7 +28532,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="243" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="12">
         <v>243</v>
       </c>
@@ -28625,7 +28615,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="244" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="12">
         <v>244</v>
       </c>
@@ -28708,7 +28698,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="245" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="12">
         <v>245</v>
       </c>
@@ -28791,7 +28781,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="246" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="12">
         <v>246</v>
       </c>
@@ -28874,7 +28864,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="247" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="12">
         <v>247</v>
       </c>
@@ -28957,7 +28947,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="248" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="12">
         <v>248</v>
       </c>
@@ -29040,7 +29030,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="249" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="12">
         <v>249</v>
       </c>
@@ -29123,7 +29113,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="250" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="12">
         <v>250</v>
       </c>
@@ -29206,7 +29196,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="251" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="12">
         <v>251</v>
       </c>
@@ -29289,7 +29279,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="252" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="12">
         <v>252</v>
       </c>
@@ -29372,7 +29362,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="253" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="12">
         <v>253</v>
       </c>
@@ -29455,7 +29445,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="254" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="12">
         <v>254</v>
       </c>
@@ -29538,7 +29528,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="255" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="12">
         <v>255</v>
       </c>
@@ -29621,7 +29611,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="256" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="12">
         <v>256</v>
       </c>
@@ -29704,7 +29694,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="257" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="12">
         <v>257</v>
       </c>
@@ -29787,7 +29777,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="258" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="12">
         <v>258</v>
       </c>
@@ -29870,7 +29860,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="259" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="12">
         <v>259</v>
       </c>
@@ -29953,7 +29943,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="260" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="12">
         <v>260</v>
       </c>
@@ -30036,7 +30026,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="261" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="12">
         <v>261</v>
       </c>
@@ -30119,7 +30109,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="262" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="12">
         <v>262</v>
       </c>
@@ -30202,7 +30192,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="263" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="12">
         <v>263</v>
       </c>
@@ -30285,7 +30275,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="264" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="12">
         <v>264</v>
       </c>
@@ -30368,7 +30358,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="265" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="12">
         <v>265</v>
       </c>
@@ -30451,7 +30441,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="266" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="12">
         <v>266</v>
       </c>
@@ -30534,7 +30524,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="267" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="12">
         <v>267</v>
       </c>
@@ -30617,7 +30607,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="268" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="12">
         <v>268</v>
       </c>
@@ -30700,7 +30690,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="269" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="12">
         <v>269</v>
       </c>
@@ -30783,7 +30773,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="270" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="12">
         <v>270</v>
       </c>
@@ -30866,7 +30856,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="271" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="12">
         <v>271</v>
       </c>
@@ -30949,7 +30939,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="272" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="12">
         <v>272</v>
       </c>
@@ -31032,7 +31022,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="273" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="12">
         <v>273</v>
       </c>
@@ -31115,7 +31105,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="274" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="12">
         <v>274</v>
       </c>
@@ -31198,7 +31188,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="275" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="12">
         <v>275</v>
       </c>
@@ -31281,7 +31271,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="276" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="12">
         <v>276</v>
       </c>
@@ -31364,7 +31354,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="277" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="12">
         <v>277</v>
       </c>
@@ -31447,7 +31437,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="278" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="12">
         <v>278</v>
       </c>
@@ -31530,7 +31520,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="279" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="12">
         <v>279</v>
       </c>
@@ -31613,7 +31603,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="280" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="12">
         <v>280</v>
       </c>
@@ -31696,7 +31686,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="281" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="12">
         <v>281</v>
       </c>
@@ -31779,7 +31769,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="282" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="12">
         <v>282</v>
       </c>
@@ -31862,7 +31852,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="283" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="12">
         <v>283</v>
       </c>
@@ -31945,7 +31935,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="284" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="12">
         <v>284</v>
       </c>
@@ -32028,7 +32018,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="285" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="12">
         <v>285</v>
       </c>
@@ -32111,7 +32101,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="286" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="12">
         <v>286</v>
       </c>
@@ -32194,7 +32184,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="287" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="12">
         <v>287</v>
       </c>
@@ -32277,7 +32267,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="288" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="12">
         <v>288</v>
       </c>
@@ -32360,7 +32350,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="289" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="12">
         <v>289</v>
       </c>
@@ -32443,7 +32433,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="290" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="12">
         <v>290</v>
       </c>
@@ -32526,7 +32516,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="291" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="12">
         <v>291</v>
       </c>
@@ -32609,7 +32599,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="292" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="12">
         <v>292</v>
       </c>
@@ -32692,7 +32682,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="293" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="12">
         <v>293</v>
       </c>
@@ -32775,7 +32765,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="294" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="12">
         <v>294</v>
       </c>
@@ -32858,7 +32848,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="295" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="12">
         <v>295</v>
       </c>
@@ -32941,7 +32931,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="296" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="12">
         <v>296</v>
       </c>
@@ -33024,7 +33014,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="297" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="12">
         <v>297</v>
       </c>
@@ -33107,7 +33097,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="298" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="12">
         <v>298</v>
       </c>
@@ -33190,7 +33180,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="299" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="12">
         <v>299</v>
       </c>
@@ -33273,7 +33263,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="300" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="12">
         <v>300</v>
       </c>
@@ -33356,7 +33346,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="301" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="12">
         <v>301</v>
       </c>
@@ -33439,7 +33429,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="302" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="12">
         <v>302</v>
       </c>
@@ -33522,7 +33512,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="303" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="12">
         <v>303</v>
       </c>
@@ -33605,7 +33595,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="304" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="12">
         <v>304</v>
       </c>
@@ -33688,7 +33678,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="305" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="12">
         <v>305</v>
       </c>
@@ -33771,7 +33761,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="306" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="12">
         <v>306</v>
       </c>
@@ -33854,7 +33844,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="307" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="12">
         <v>307</v>
       </c>
@@ -33937,7 +33927,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="308" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="12">
         <v>308</v>
       </c>
@@ -34020,7 +34010,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="309" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="12">
         <v>309</v>
       </c>
@@ -34103,7 +34093,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="310" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="12">
         <v>310</v>
       </c>
@@ -34186,7 +34176,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="311" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="12">
         <v>311</v>
       </c>
@@ -34269,7 +34259,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="312" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="12">
         <v>312</v>
       </c>
@@ -34352,7 +34342,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="313" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="12">
         <v>313</v>
       </c>
@@ -34435,7 +34425,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="314" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="12">
         <v>314</v>
       </c>
@@ -34518,7 +34508,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="315" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="12">
         <v>315</v>
       </c>
@@ -34601,7 +34591,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="316" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="12">
         <v>316</v>
       </c>
@@ -34684,7 +34674,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="317" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="12">
         <v>317</v>
       </c>
@@ -34767,7 +34757,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="318" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="12">
         <v>318</v>
       </c>
@@ -34850,7 +34840,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="319" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="12">
         <v>319</v>
       </c>
@@ -34933,7 +34923,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="320" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="12">
         <v>320</v>
       </c>
@@ -35016,7 +35006,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="321" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="12">
         <v>321</v>
       </c>
@@ -35099,7 +35089,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="322" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="12">
         <v>322</v>
       </c>
@@ -35182,7 +35172,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="323" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="12">
         <v>323</v>
       </c>
@@ -35265,7 +35255,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="324" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="12">
         <v>324</v>
       </c>
@@ -35348,7 +35338,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="325" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="12">
         <v>325</v>
       </c>
@@ -35431,7 +35421,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="326" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="12">
         <v>326</v>
       </c>
@@ -35514,7 +35504,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="327" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="12">
         <v>327</v>
       </c>
@@ -35597,7 +35587,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="328" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="12">
         <v>328</v>
       </c>
@@ -35680,7 +35670,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="329" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="12">
         <v>329</v>
       </c>
@@ -35763,7 +35753,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="330" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="12">
         <v>330</v>
       </c>
@@ -35846,7 +35836,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="331" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="12">
         <v>331</v>
       </c>
@@ -35929,7 +35919,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="332" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="12">
         <v>332</v>
       </c>
@@ -36012,7 +36002,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="333" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="12">
         <v>333</v>
       </c>
@@ -36095,7 +36085,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="334" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="12">
         <v>334</v>
       </c>
@@ -36178,7 +36168,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="335" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="12">
         <v>335</v>
       </c>
@@ -36261,7 +36251,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="336" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="12">
         <v>336</v>
       </c>
@@ -36344,7 +36334,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="337" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="12">
         <v>337</v>
       </c>
@@ -36427,7 +36417,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="338" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="12">
         <v>338</v>
       </c>
@@ -36510,7 +36500,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="339" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="12">
         <v>339</v>
       </c>
@@ -36593,7 +36583,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="340" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="12">
         <v>340</v>
       </c>
@@ -36676,7 +36666,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="341" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="12">
         <v>341</v>
       </c>
@@ -36759,7 +36749,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="342" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="12">
         <v>342</v>
       </c>
@@ -36842,7 +36832,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="343" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="12">
         <v>343</v>
       </c>
@@ -36925,7 +36915,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="344" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="12">
         <v>344</v>
       </c>
@@ -37008,7 +36998,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="345" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="12">
         <v>345</v>
       </c>
@@ -37091,7 +37081,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="346" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="12">
         <v>346</v>
       </c>
@@ -37174,7 +37164,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="347" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="12">
         <v>347</v>
       </c>
@@ -37257,7 +37247,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="348" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="12">
         <v>348</v>
       </c>
@@ -37340,7 +37330,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="349" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="12">
         <v>349</v>
       </c>
@@ -37423,7 +37413,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="350" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="12">
         <v>350</v>
       </c>
@@ -37506,7 +37496,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="351" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="12">
         <v>351</v>
       </c>
@@ -37589,7 +37579,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="352" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="12">
         <v>352</v>
       </c>
@@ -37672,7 +37662,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="353" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="12">
         <v>353</v>
       </c>
@@ -37755,7 +37745,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="354" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="12">
         <v>354</v>
       </c>
@@ -37838,7 +37828,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="355" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="12">
         <v>355</v>
       </c>
@@ -37921,7 +37911,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="356" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="12">
         <v>356</v>
       </c>
@@ -38004,7 +37994,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="357" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="12">
         <v>357</v>
       </c>
@@ -38087,7 +38077,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="358" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="12">
         <v>358</v>
       </c>
@@ -38170,7 +38160,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="359" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="12">
         <v>359</v>
       </c>
@@ -38253,7 +38243,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="360" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="12">
         <v>360</v>
       </c>
@@ -38336,7 +38326,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="361" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="12">
         <v>361</v>
       </c>
@@ -38419,7 +38409,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="362" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="12">
         <v>362</v>
       </c>
@@ -38502,7 +38492,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="363" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="12">
         <v>363</v>
       </c>
@@ -38585,7 +38575,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="364" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="12">
         <v>364</v>
       </c>
@@ -38668,7 +38658,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="365" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="12">
         <v>365</v>
       </c>
@@ -38751,7 +38741,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="366" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="12">
         <v>366</v>
       </c>
@@ -38834,7 +38824,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="367" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="12">
         <v>367</v>
       </c>
@@ -38917,7 +38907,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="368" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="12">
         <v>368</v>
       </c>
@@ -39000,7 +38990,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="369" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="12">
         <v>369</v>
       </c>
@@ -39083,7 +39073,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="370" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="12">
         <v>370</v>
       </c>
@@ -39166,7 +39156,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="371" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="12">
         <v>371</v>
       </c>
@@ -39249,7 +39239,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="372" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="12">
         <v>372</v>
       </c>
@@ -39332,7 +39322,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="373" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="12">
         <v>373</v>
       </c>
@@ -39415,7 +39405,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="374" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="12">
         <v>374</v>
       </c>
@@ -39498,7 +39488,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="375" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="12">
         <v>375</v>
       </c>
@@ -39581,7 +39571,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="376" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="12">
         <v>376</v>
       </c>
@@ -39664,7 +39654,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="377" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="12">
         <v>377</v>
       </c>
@@ -39747,7 +39737,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="378" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="12">
         <v>378</v>
       </c>
@@ -39830,7 +39820,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="379" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="12">
         <v>379</v>
       </c>
@@ -39913,7 +39903,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="380" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="12">
         <v>380</v>
       </c>
@@ -39996,7 +39986,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="381" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="12">
         <v>381</v>
       </c>
@@ -40079,7 +40069,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="382" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="12">
         <v>382</v>
       </c>
@@ -40162,7 +40152,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="383" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="12">
         <v>383</v>
       </c>
@@ -40245,7 +40235,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="384" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="12">
         <v>384</v>
       </c>
@@ -40328,7 +40318,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="385" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="12">
         <v>385</v>
       </c>
@@ -40411,7 +40401,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="386" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="12">
         <v>386</v>
       </c>
@@ -40494,7 +40484,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="387" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="12">
         <v>387</v>
       </c>
@@ -40577,7 +40567,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="388" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="12">
         <v>388</v>
       </c>
@@ -40660,7 +40650,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="389" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="12">
         <v>389</v>
       </c>
@@ -40743,7 +40733,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="390" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="12">
         <v>390</v>
       </c>
@@ -40826,7 +40816,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="391" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="12">
         <v>391</v>
       </c>
@@ -40909,7 +40899,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="392" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="12">
         <v>392</v>
       </c>
@@ -40992,7 +40982,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="393" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="12">
         <v>393</v>
       </c>
@@ -41075,7 +41065,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="394" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="12">
         <v>394</v>
       </c>
@@ -41158,7 +41148,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="395" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="12">
         <v>395</v>
       </c>
@@ -41241,7 +41231,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="396" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="12">
         <v>396</v>
       </c>
@@ -41324,7 +41314,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="397" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="12">
         <v>397</v>
       </c>
@@ -41407,7 +41397,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="398" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="12">
         <v>398</v>
       </c>
@@ -41490,7 +41480,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="399" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="12">
         <v>399</v>
       </c>
@@ -41573,7 +41563,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="400" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="12">
         <v>400</v>
       </c>
@@ -41656,7 +41646,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="401" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="12">
         <v>401</v>
       </c>
@@ -41739,7 +41729,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="402" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="12">
         <v>402</v>
       </c>
@@ -41822,7 +41812,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="403" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="12">
         <v>403</v>
       </c>
@@ -41905,7 +41895,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="404" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="12">
         <v>404</v>
       </c>
@@ -41988,7 +41978,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="405" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="12">
         <v>405</v>
       </c>
@@ -42071,7 +42061,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="406" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="12">
         <v>406</v>
       </c>
@@ -42154,7 +42144,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="407" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="12">
         <v>407</v>
       </c>
@@ -42237,7 +42227,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="408" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="12">
         <v>408</v>
       </c>
@@ -42320,7 +42310,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="409" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="12">
         <v>409</v>
       </c>
@@ -42403,7 +42393,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="410" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="12">
         <v>410</v>
       </c>
@@ -42486,7 +42476,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="411" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="12">
         <v>411</v>
       </c>
@@ -42569,7 +42559,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="412" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="12">
         <v>412</v>
       </c>
@@ -42652,7 +42642,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="413" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="12">
         <v>413</v>
       </c>
@@ -42735,7 +42725,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="414" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="12">
         <v>414</v>
       </c>
@@ -42818,7 +42808,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="415" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="12">
         <v>415</v>
       </c>
@@ -42901,7 +42891,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="416" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="12">
         <v>416</v>
       </c>
@@ -42984,7 +42974,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="417" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="12">
         <v>417</v>
       </c>
@@ -43067,7 +43057,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="418" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="12">
         <v>418</v>
       </c>
@@ -43150,7 +43140,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="419" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="12">
         <v>419</v>
       </c>
@@ -43233,7 +43223,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="420" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="12">
         <v>420</v>
       </c>
@@ -43316,7 +43306,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="421" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="12">
         <v>421</v>
       </c>
@@ -43399,7 +43389,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="422" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="12">
         <v>422</v>
       </c>
@@ -43482,7 +43472,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="423" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="12">
         <v>423</v>
       </c>
@@ -43565,7 +43555,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="424" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="12">
         <v>424</v>
       </c>
@@ -43648,7 +43638,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="425" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="12">
         <v>425</v>
       </c>
@@ -43731,7 +43721,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="426" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="12">
         <v>426</v>
       </c>
@@ -43814,7 +43804,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="427" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="12">
         <v>427</v>
       </c>
@@ -43897,7 +43887,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="428" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="12">
         <v>428</v>
       </c>
@@ -43980,7 +43970,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="429" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="12">
         <v>429</v>
       </c>
@@ -44063,7 +44053,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="430" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="12">
         <v>430</v>
       </c>
@@ -44146,7 +44136,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="431" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="12">
         <v>431</v>
       </c>
@@ -44229,7 +44219,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="432" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="12">
         <v>432</v>
       </c>
@@ -44312,7 +44302,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="433" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="12">
         <v>433</v>
       </c>
@@ -44395,7 +44385,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="434" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="12">
         <v>434</v>
       </c>
@@ -44478,7 +44468,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="435" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="12">
         <v>435</v>
       </c>
@@ -44561,7 +44551,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="436" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="12">
         <v>436</v>
       </c>
@@ -44644,7 +44634,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="437" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="12">
         <v>437</v>
       </c>
@@ -44727,7 +44717,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="438" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="12">
         <v>438</v>
       </c>
@@ -44810,7 +44800,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="439" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="12">
         <v>439</v>
       </c>
@@ -44893,7 +44883,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="440" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="12">
         <v>440</v>
       </c>
@@ -44976,7 +44966,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="441" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="12">
         <v>441</v>
       </c>
@@ -45059,7 +45049,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="442" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="12">
         <v>442</v>
       </c>
@@ -45142,7 +45132,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="443" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="12">
         <v>443</v>
       </c>
@@ -45225,7 +45215,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="444" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="12">
         <v>444</v>
       </c>
@@ -45308,7 +45298,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="445" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="12">
         <v>445</v>
       </c>
@@ -45391,7 +45381,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="446" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="12">
         <v>446</v>
       </c>
@@ -45474,7 +45464,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="447" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="12">
         <v>447</v>
       </c>
@@ -45557,7 +45547,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="448" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="12">
         <v>448</v>
       </c>
@@ -45640,7 +45630,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="449" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="12">
         <v>449</v>
       </c>
@@ -45723,7 +45713,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="450" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="12">
         <v>450</v>
       </c>
@@ -45806,7 +45796,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="451" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="12">
         <v>451</v>
       </c>
@@ -45889,7 +45879,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="452" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="12">
         <v>452</v>
       </c>
@@ -45972,7 +45962,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="453" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="12">
         <v>453</v>
       </c>
@@ -46055,7 +46045,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="454" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="12">
         <v>454</v>
       </c>
@@ -46138,7 +46128,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="455" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="12">
         <v>455</v>
       </c>
@@ -46221,7 +46211,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="456" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="12">
         <v>456</v>
       </c>
@@ -46304,7 +46294,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="457" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="12">
         <v>457</v>
       </c>
@@ -46387,7 +46377,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="458" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="12">
         <v>458</v>
       </c>
@@ -46470,7 +46460,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="459" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="12">
         <v>459</v>
       </c>
@@ -46553,7 +46543,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="460" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="12">
         <v>460</v>
       </c>
@@ -46636,7 +46626,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="461" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="12">
         <v>461</v>
       </c>
@@ -46719,7 +46709,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="462" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="12">
         <v>462</v>
       </c>
@@ -46802,7 +46792,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="463" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="12">
         <v>463</v>
       </c>
@@ -46885,7 +46875,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="464" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="12">
         <v>464</v>
       </c>
@@ -46968,7 +46958,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="465" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="12">
         <v>465</v>
       </c>
@@ -47051,7 +47041,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="466" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="12">
         <v>466</v>
       </c>
@@ -47134,7 +47124,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="467" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="12">
         <v>467</v>
       </c>
@@ -47217,7 +47207,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="468" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="12">
         <v>468</v>
       </c>
@@ -47300,7 +47290,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="469" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="12">
         <v>469</v>
       </c>
@@ -47383,7 +47373,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="470" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="12">
         <v>470</v>
       </c>
@@ -47466,7 +47456,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="471" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="12">
         <v>471</v>
       </c>
@@ -47549,7 +47539,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="472" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="12">
         <v>472</v>
       </c>
@@ -47632,7 +47622,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="473" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="12">
         <v>473</v>
       </c>
@@ -47715,7 +47705,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="474" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="12">
         <v>474</v>
       </c>
@@ -47798,7 +47788,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="475" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="12">
         <v>475</v>
       </c>
@@ -47881,7 +47871,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="476" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="12">
         <v>476</v>
       </c>
@@ -47964,7 +47954,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="477" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="12">
         <v>477</v>
       </c>
@@ -48047,7 +48037,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="478" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="12">
         <v>478</v>
       </c>
@@ -48130,7 +48120,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="479" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="12">
         <v>479</v>
       </c>
@@ -48213,7 +48203,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="480" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="12">
         <v>480</v>
       </c>
@@ -48296,7 +48286,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="481" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="12">
         <v>481</v>
       </c>
@@ -48379,7 +48369,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="482" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="12">
         <v>482</v>
       </c>
@@ -48462,7 +48452,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="483" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="12">
         <v>483</v>
       </c>
@@ -48545,7 +48535,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="484" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="12">
         <v>484</v>
       </c>
@@ -48628,7 +48618,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="485" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="12">
         <v>485</v>
       </c>
@@ -48711,7 +48701,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="486" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="12">
         <v>486</v>
       </c>
@@ -48794,7 +48784,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="487" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="12">
         <v>487</v>
       </c>
@@ -48877,7 +48867,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="488" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="12">
         <v>488</v>
       </c>
@@ -48960,7 +48950,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="489" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="12">
         <v>489</v>
       </c>
@@ -49043,7 +49033,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="490" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="12">
         <v>490</v>
       </c>
@@ -49126,7 +49116,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="491" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="12">
         <v>491</v>
       </c>
@@ -49209,7 +49199,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="492" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="12">
         <v>492</v>
       </c>
@@ -49292,7 +49282,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="493" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="12">
         <v>493</v>
       </c>
@@ -49375,7 +49365,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="494" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="12">
         <v>494</v>
       </c>
@@ -49458,7 +49448,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="495" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="12">
         <v>495</v>
       </c>
@@ -49541,7 +49531,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="496" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="12">
         <v>496</v>
       </c>
@@ -49624,7 +49614,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="497" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="12">
         <v>497</v>
       </c>
@@ -49707,7 +49697,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="498" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="12">
         <v>498</v>
       </c>
@@ -49790,7 +49780,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="499" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="12">
         <v>499</v>
       </c>
@@ -49873,7 +49863,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="500" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="12">
         <v>500</v>
       </c>
@@ -49956,7 +49946,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="501" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="12">
         <v>501</v>
       </c>
@@ -50039,7 +50029,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="502" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="12">
         <v>502</v>
       </c>
@@ -50122,7 +50112,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="503" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="12">
         <v>503</v>
       </c>
@@ -50205,7 +50195,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="504" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="12">
         <v>504</v>
       </c>
@@ -50288,7 +50278,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="505" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="12">
         <v>505</v>
       </c>
@@ -50371,7 +50361,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="506" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="12">
         <v>506</v>
       </c>
@@ -50454,7 +50444,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="507" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="12">
         <v>507</v>
       </c>
@@ -50537,7 +50527,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="508" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="12">
         <v>508</v>
       </c>
@@ -50620,7 +50610,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="509" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="12">
         <v>509</v>
       </c>
@@ -50703,7 +50693,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="510" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="12">
         <v>510</v>
       </c>
@@ -50786,7 +50776,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="511" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="12">
         <v>511</v>
       </c>
@@ -50869,7 +50859,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="512" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="12">
         <v>512</v>
       </c>
@@ -50952,7 +50942,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="513" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="12">
         <v>513</v>
       </c>
@@ -51035,7 +51025,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="514" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="12">
         <v>514</v>
       </c>
@@ -51118,7 +51108,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="515" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="12">
         <v>515</v>
       </c>
@@ -51201,7 +51191,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="516" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="12">
         <v>516</v>
       </c>
@@ -51284,7 +51274,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="517" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="12">
         <v>517</v>
       </c>
@@ -51367,7 +51357,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="518" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="12">
         <v>518</v>
       </c>
@@ -51450,7 +51440,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="519" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="12">
         <v>519</v>
       </c>
@@ -51533,7 +51523,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="520" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="12">
         <v>520</v>
       </c>
@@ -51616,7 +51606,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="521" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="12">
         <v>521</v>
       </c>
@@ -51699,7 +51689,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="522" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="12">
         <v>522</v>
       </c>
@@ -51782,7 +51772,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="523" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="12">
         <v>523</v>
       </c>
@@ -51865,7 +51855,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="524" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="12">
         <v>524</v>
       </c>
@@ -51948,7 +51938,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="525" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="12">
         <v>525</v>
       </c>
@@ -52031,7 +52021,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="526" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="12">
         <v>526</v>
       </c>
@@ -52114,7 +52104,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="527" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="12">
         <v>527</v>
       </c>
@@ -52197,7 +52187,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="528" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="12">
         <v>528</v>
       </c>
@@ -52280,7 +52270,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="529" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="12">
         <v>529</v>
       </c>
@@ -52363,7 +52353,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="530" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="12">
         <v>530</v>
       </c>
@@ -52446,7 +52436,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="531" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="12">
         <v>531</v>
       </c>
@@ -52529,7 +52519,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="532" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="12">
         <v>532</v>
       </c>
@@ -52612,7 +52602,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="533" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="12">
         <v>533</v>
       </c>
@@ -52695,7 +52685,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="534" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="12">
         <v>534</v>
       </c>
@@ -52778,7 +52768,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="535" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="12">
         <v>535</v>
       </c>
@@ -52861,7 +52851,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="536" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="12">
         <v>536</v>
       </c>
@@ -52944,7 +52934,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="537" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="12">
         <v>537</v>
       </c>
@@ -53027,7 +53017,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="538" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="12">
         <v>538</v>
       </c>
@@ -53110,7 +53100,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="539" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="12">
         <v>539</v>
       </c>
@@ -53193,7 +53183,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="540" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="12">
         <v>540</v>
       </c>
@@ -53276,7 +53266,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="541" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="12">
         <v>541</v>
       </c>
@@ -53359,7 +53349,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="542" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="12">
         <v>542</v>
       </c>
@@ -53442,7 +53432,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="543" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="12">
         <v>543</v>
       </c>
@@ -53525,7 +53515,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="544" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="12">
         <v>544</v>
       </c>
@@ -53608,7 +53598,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="545" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="12">
         <v>545</v>
       </c>
@@ -53691,7 +53681,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="546" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="12">
         <v>546</v>
       </c>
@@ -53774,7 +53764,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="547" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="12">
         <v>547</v>
       </c>
@@ -53857,7 +53847,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="548" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="12">
         <v>548</v>
       </c>
@@ -53940,7 +53930,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="549" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="12">
         <v>549</v>
       </c>
@@ -54023,7 +54013,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="550" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="12">
         <v>550</v>
       </c>
@@ -54106,7 +54096,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="551" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="12">
         <v>551</v>
       </c>
@@ -54189,7 +54179,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="552" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="12">
         <v>552</v>
       </c>
@@ -54272,7 +54262,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="553" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="12">
         <v>553</v>
       </c>
@@ -54355,7 +54345,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="554" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="12">
         <v>554</v>
       </c>
@@ -54438,7 +54428,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="555" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="12">
         <v>555</v>
       </c>
@@ -54521,7 +54511,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="556" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="12">
         <v>556</v>
       </c>
@@ -54604,7 +54594,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="557" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="12">
         <v>557</v>
       </c>
@@ -54687,7 +54677,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="558" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="12">
         <v>558</v>
       </c>
@@ -54770,7 +54760,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="559" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="12">
         <v>559</v>
       </c>
@@ -54853,7 +54843,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="560" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="12">
         <v>560</v>
       </c>
@@ -54936,7 +54926,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="561" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="12">
         <v>561</v>
       </c>
@@ -55019,7 +55009,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="562" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="12">
         <v>562</v>
       </c>
@@ -55102,7 +55092,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="563" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="12">
         <v>563</v>
       </c>
@@ -55185,7 +55175,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="564" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="12">
         <v>564</v>
       </c>
@@ -55268,7 +55258,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="565" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="12">
         <v>565</v>
       </c>
@@ -55351,7 +55341,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="566" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="12">
         <v>566</v>
       </c>
@@ -55434,7 +55424,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="567" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="12">
         <v>567</v>
       </c>
@@ -55517,7 +55507,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="568" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="12">
         <v>568</v>
       </c>
@@ -55600,7 +55590,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="569" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="12">
         <v>569</v>
       </c>
@@ -55683,7 +55673,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="570" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="12">
         <v>570</v>
       </c>
@@ -55766,7 +55756,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="571" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="12">
         <v>571</v>
       </c>
@@ -55849,7 +55839,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="572" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="12">
         <v>572</v>
       </c>
@@ -55932,7 +55922,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="573" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="12">
         <v>573</v>
       </c>
@@ -56015,7 +56005,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="574" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="12">
         <v>574</v>
       </c>
@@ -56098,7 +56088,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="575" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="12">
         <v>575</v>
       </c>
@@ -56181,7 +56171,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="576" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="12">
         <v>576</v>
       </c>
@@ -56264,7 +56254,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="577" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="12">
         <v>577</v>
       </c>
@@ -56347,7 +56337,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="578" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="12">
         <v>578</v>
       </c>
@@ -56430,7 +56420,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="579" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="12">
         <v>579</v>
       </c>
@@ -56513,7 +56503,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="580" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="12">
         <v>580</v>
       </c>
@@ -56596,7 +56586,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="581" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="12">
         <v>581</v>
       </c>
@@ -56679,7 +56669,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="582" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="12">
         <v>582</v>
       </c>
@@ -56762,7 +56752,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="583" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="12">
         <v>583</v>
       </c>
@@ -56845,7 +56835,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="584" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="12">
         <v>584</v>
       </c>
@@ -56928,7 +56918,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="585" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="12">
         <v>585</v>
       </c>
@@ -57011,7 +57001,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="586" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="12">
         <v>586</v>
       </c>
@@ -57094,7 +57084,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="587" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="12">
         <v>587</v>
       </c>
@@ -57177,7 +57167,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="588" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="12">
         <v>588</v>
       </c>
@@ -57260,7 +57250,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="589" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="12">
         <v>589</v>
       </c>
@@ -57343,7 +57333,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="590" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="12">
         <v>590</v>
       </c>
@@ -57426,7 +57416,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="591" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="12">
         <v>591</v>
       </c>
@@ -57509,7 +57499,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="592" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="12">
         <v>592</v>
       </c>
@@ -57592,7 +57582,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="593" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="12">
         <v>593</v>
       </c>
@@ -57675,7 +57665,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="594" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="12">
         <v>594</v>
       </c>
@@ -57758,7 +57748,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="595" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="12">
         <v>595</v>
       </c>
@@ -57841,7 +57831,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="596" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="12">
         <v>596</v>
       </c>
@@ -57924,7 +57914,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="597" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="12">
         <v>597</v>
       </c>
@@ -58007,7 +57997,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="598" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="12">
         <v>598</v>
       </c>
@@ -58090,7 +58080,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="599" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="12">
         <v>599</v>
       </c>
@@ -58173,7 +58163,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="600" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="12">
         <v>600</v>
       </c>
@@ -58256,7 +58246,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="601" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="12">
         <v>601</v>
       </c>
@@ -58339,7 +58329,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="602" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="12">
         <v>602</v>
       </c>
@@ -58422,7 +58412,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="603" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="12">
         <v>603</v>
       </c>
@@ -58505,7 +58495,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="604" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="12">
         <v>604</v>
       </c>
@@ -58588,7 +58578,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="605" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="12">
         <v>605</v>
       </c>
@@ -58671,7 +58661,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="606" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="12">
         <v>606</v>
       </c>
@@ -58754,7 +58744,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="607" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="12">
         <v>607</v>
       </c>
@@ -58837,7 +58827,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="608" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="12">
         <v>608</v>
       </c>
@@ -58920,7 +58910,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="609" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="12">
         <v>609</v>
       </c>
@@ -59003,7 +58993,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="610" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="12">
         <v>610</v>
       </c>
@@ -59086,7 +59076,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="611" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="12">
         <v>611</v>
       </c>
@@ -59169,7 +59159,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="612" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="12">
         <v>612</v>
       </c>
@@ -59252,7 +59242,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="613" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="12">
         <v>613</v>
       </c>
@@ -59335,7 +59325,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="614" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="12">
         <v>614</v>
       </c>
@@ -59418,7 +59408,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="615" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="12">
         <v>615</v>
       </c>
@@ -59501,7 +59491,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="616" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="12">
         <v>616</v>
       </c>
@@ -59584,7 +59574,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="617" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="12">
         <v>617</v>
       </c>
@@ -59667,7 +59657,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="618" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="12">
         <v>618</v>
       </c>
@@ -59750,7 +59740,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="619" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="12">
         <v>619</v>
       </c>
@@ -59833,7 +59823,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="620" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="12">
         <v>620</v>
       </c>
@@ -59916,7 +59906,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="621" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="12">
         <v>621</v>
       </c>
@@ -59999,7 +59989,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="622" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="12">
         <v>622</v>
       </c>
@@ -60082,7 +60072,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="623" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="12">
         <v>623</v>
       </c>
@@ -60165,7 +60155,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="624" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="12">
         <v>624</v>
       </c>
@@ -60248,7 +60238,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="625" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="12">
         <v>625</v>
       </c>
@@ -60331,7 +60321,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="626" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="12">
         <v>626</v>
       </c>
@@ -60414,7 +60404,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="627" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="12">
         <v>627</v>
       </c>
@@ -60497,7 +60487,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="628" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" s="12">
         <v>628</v>
       </c>
@@ -60580,7 +60570,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="629" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" s="12">
         <v>629</v>
       </c>
@@ -60663,7 +60653,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="630" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" s="12">
         <v>630</v>
       </c>
@@ -60746,7 +60736,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="631" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="12">
         <v>631</v>
       </c>
@@ -60829,7 +60819,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="632" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" s="12">
         <v>632</v>
       </c>
@@ -60912,7 +60902,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="633" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" s="12">
         <v>633</v>
       </c>
@@ -60995,7 +60985,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="634" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" s="12">
         <v>634</v>
       </c>
@@ -61078,7 +61068,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="635" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" s="12">
         <v>635</v>
       </c>
@@ -61161,7 +61151,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="636" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="12">
         <v>636</v>
       </c>
@@ -61244,7 +61234,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="637" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" s="12">
         <v>637</v>
       </c>
@@ -61327,7 +61317,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="638" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" s="12">
         <v>638</v>
       </c>
@@ -61410,7 +61400,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="639" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" s="12">
         <v>639</v>
       </c>
@@ -61493,7 +61483,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="640" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="12">
         <v>640</v>
       </c>
@@ -61576,7 +61566,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="641" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="12">
         <v>641</v>
       </c>
@@ -61659,7 +61649,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="642" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="12">
         <v>642</v>
       </c>
@@ -61742,7 +61732,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="643" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="12">
         <v>643</v>
       </c>
@@ -61825,7 +61815,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="644" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="12">
         <v>644</v>
       </c>
@@ -61908,7 +61898,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="645" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" s="12">
         <v>645</v>
       </c>
@@ -61991,7 +61981,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="646" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" s="12">
         <v>646</v>
       </c>
@@ -62074,7 +62064,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="647" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="12">
         <v>647</v>
       </c>
@@ -62157,7 +62147,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="648" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="12">
         <v>648</v>
       </c>
@@ -62240,7 +62230,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="649" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="12">
         <v>649</v>
       </c>
@@ -62323,7 +62313,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="650" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="12">
         <v>650</v>
       </c>
@@ -62406,7 +62396,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="651" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="12">
         <v>651</v>
       </c>
@@ -62489,7 +62479,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="652" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="12">
         <v>652</v>
       </c>
@@ -62572,7 +62562,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="653" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="12">
         <v>653</v>
       </c>
@@ -62655,7 +62645,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="654" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" s="12">
         <v>654</v>
       </c>
@@ -62738,7 +62728,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="655" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="12">
         <v>655</v>
       </c>
@@ -62821,7 +62811,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="656" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="12">
         <v>656</v>
       </c>
@@ -62904,7 +62894,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="657" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" s="12">
         <v>657</v>
       </c>
@@ -62987,7 +62977,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="658" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" s="12">
         <v>658</v>
       </c>
@@ -63070,7 +63060,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="659" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" s="12">
         <v>659</v>
       </c>
@@ -63153,7 +63143,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="660" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" s="12">
         <v>660</v>
       </c>
@@ -63236,7 +63226,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="661" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" s="12">
         <v>661</v>
       </c>
@@ -63319,7 +63309,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="662" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="12">
         <v>662</v>
       </c>
@@ -63402,7 +63392,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="663" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" s="12">
         <v>663</v>
       </c>
@@ -63485,7 +63475,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="664" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664" s="12">
         <v>664</v>
       </c>
@@ -63568,7 +63558,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="665" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665" s="12">
         <v>665</v>
       </c>
@@ -63651,7 +63641,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="666" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666" s="12">
         <v>666</v>
       </c>
@@ -63734,7 +63724,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="667" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" s="12">
         <v>667</v>
       </c>
@@ -63817,7 +63807,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="668" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668" s="12">
         <v>668</v>
       </c>
@@ -63900,7 +63890,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="669" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" s="12">
         <v>669</v>
       </c>
@@ -63983,7 +63973,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="670" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" s="12">
         <v>670</v>
       </c>
@@ -64066,7 +64056,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="671" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" s="12">
         <v>671</v>
       </c>
@@ -64149,7 +64139,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="672" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" s="12">
         <v>672</v>
       </c>
@@ -64232,7 +64222,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="673" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="12">
         <v>673</v>
       </c>
@@ -64315,7 +64305,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="674" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" s="12">
         <v>674</v>
       </c>
@@ -64398,7 +64388,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="675" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675" s="12">
         <v>675</v>
       </c>
@@ -64481,7 +64471,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="676" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" s="12">
         <v>676</v>
       </c>
@@ -64564,7 +64554,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="677" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" s="12">
         <v>677</v>
       </c>
@@ -64647,7 +64637,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="678" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="12">
         <v>678</v>
       </c>
@@ -64730,7 +64720,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="679" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" s="12">
         <v>679</v>
       </c>
@@ -64813,7 +64803,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="680" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" s="12">
         <v>680</v>
       </c>
@@ -64896,7 +64886,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="681" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" s="12">
         <v>681</v>
       </c>
@@ -64979,7 +64969,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="682" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" s="12">
         <v>682</v>
       </c>
@@ -65062,7 +65052,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="683" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" s="12">
         <v>683</v>
       </c>
@@ -65145,7 +65135,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="684" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" s="12">
         <v>684</v>
       </c>
@@ -65228,7 +65218,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="685" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" s="12">
         <v>685</v>
       </c>
@@ -65311,7 +65301,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="686" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" s="12">
         <v>686</v>
       </c>
@@ -65394,7 +65384,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="687" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" s="12">
         <v>687</v>
       </c>
@@ -65477,7 +65467,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="688" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" s="12">
         <v>688</v>
       </c>
@@ -65560,7 +65550,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="689" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" s="12">
         <v>689</v>
       </c>
@@ -65643,7 +65633,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="690" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="12">
         <v>690</v>
       </c>
@@ -65726,7 +65716,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="691" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="12">
         <v>691</v>
       </c>
@@ -65809,7 +65799,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="692" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="12">
         <v>692</v>
       </c>
@@ -65892,7 +65882,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="693" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" s="12">
         <v>693</v>
       </c>
@@ -65975,7 +65965,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="694" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" s="12">
         <v>694</v>
       </c>
@@ -66058,7 +66048,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="695" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" s="12">
         <v>695</v>
       </c>
@@ -66141,7 +66131,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="696" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" s="12">
         <v>696</v>
       </c>
@@ -66224,7 +66214,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="697" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="12">
         <v>697</v>
       </c>
@@ -66307,7 +66297,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="698" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="12">
         <v>698</v>
       </c>
@@ -66390,7 +66380,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="699" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" s="12">
         <v>699</v>
       </c>
@@ -66473,7 +66463,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="700" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="12">
         <v>700</v>
       </c>
@@ -66556,7 +66546,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="701" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="12">
         <v>701</v>
       </c>
@@ -66639,7 +66629,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="702" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="12">
         <v>702</v>
       </c>
@@ -66722,7 +66712,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="703" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="12">
         <v>703</v>
       </c>
@@ -66805,7 +66795,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="704" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="12">
         <v>704</v>
       </c>
@@ -66888,7 +66878,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="705" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="12">
         <v>705</v>
       </c>
@@ -66971,7 +66961,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="706" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="12">
         <v>706</v>
       </c>
@@ -67054,7 +67044,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="707" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="12">
         <v>707</v>
       </c>
@@ -67137,7 +67127,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="708" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="12">
         <v>708</v>
       </c>
@@ -67220,7 +67210,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="709" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="12">
         <v>709</v>
       </c>
@@ -67303,7 +67293,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="710" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="12">
         <v>710</v>
       </c>
@@ -67386,7 +67376,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="711" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="12">
         <v>711</v>
       </c>
@@ -67469,7 +67459,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="712" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="12">
         <v>712</v>
       </c>
@@ -67552,7 +67542,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="713" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="12">
         <v>713</v>
       </c>
@@ -67635,7 +67625,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="714" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="12">
         <v>714</v>
       </c>
@@ -67718,7 +67708,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="715" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="12">
         <v>715</v>
       </c>
@@ -67801,7 +67791,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="716" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716" s="12">
         <v>716</v>
       </c>
@@ -67884,7 +67874,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="717" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A717" s="12">
         <v>717</v>
       </c>
@@ -67967,7 +67957,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="718" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718" s="12">
         <v>718</v>
       </c>
@@ -68050,7 +68040,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="719" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A719" s="12">
         <v>719</v>
       </c>
@@ -68133,7 +68123,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="720" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720" s="12">
         <v>720</v>
       </c>
@@ -68216,7 +68206,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="721" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="12">
         <v>721</v>
       </c>
@@ -68299,7 +68289,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="722" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722" s="12">
         <v>722</v>
       </c>
@@ -68382,7 +68372,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="723" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723" s="12">
         <v>723</v>
       </c>
@@ -68465,7 +68455,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="724" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A724" s="12">
         <v>724</v>
       </c>
@@ -68548,7 +68538,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="725" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A725" s="12">
         <v>725</v>
       </c>
@@ -68631,7 +68621,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="726" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726" s="12">
         <v>726</v>
       </c>
@@ -68714,7 +68704,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="727" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A727" s="12">
         <v>727</v>
       </c>
@@ -68797,7 +68787,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="728" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A728" s="12">
         <v>728</v>
       </c>
@@ -68880,7 +68870,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="729" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A729" s="12">
         <v>729</v>
       </c>
@@ -68963,7 +68953,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="730" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A730" s="12">
         <v>730</v>
       </c>
@@ -69046,7 +69036,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="731" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A731" s="12">
         <v>731</v>
       </c>
@@ -69129,7 +69119,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="732" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732" s="12">
         <v>732</v>
       </c>
@@ -69218,65 +69208,65 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="13" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB2:XFD2 P2:AA732 K3:K4 M3:M4 D4:D732 B2:Q2 D3:E3">
-    <cfRule type="cellIs" dxfId="1" priority="9" operator="equal">
+  <conditionalFormatting sqref="B2:Q2 AB2:XFD2 P2:AA732 D3:E3 K3:K4 M3:M4 D4:D732">
+    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1 F1">
-    <cfRule type="cellIs" dxfId="12" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="20" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="11" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="10" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="8" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="7" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="5" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_5I.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_5I.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="EstaPastaDeTrabalho"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E4C4B1-1F81-4F9F-99EB-8692886F4018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A74BAE-52F0-490F-8FA6-FCC2089FF67D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -5985,63 +5985,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{8576210E-162F-453B-B886-CD2163C7562E}"/>
   </cellStyles>
-  <dxfs count="28">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="22">
     <dxf>
       <font>
         <b val="0"/>
@@ -6769,7 +6713,7 @@
       </c>
       <c r="B18" s="4">
         <f ca="1">NOW()</f>
-        <v>46167.414135069441</v>
+        <v>46214.346964236109</v>
       </c>
       <c r="C18" s="45" t="s">
         <v>1542</v>
@@ -7474,7 +7418,7 @@
         <v>33</v>
       </c>
       <c r="L7" s="61" t="str">
-        <f t="shared" ref="L2:N17" si="4">CONCATENATE("", C7)</f>
+        <f t="shared" ref="L7:N17" si="4">CONCATENATE("", C7)</f>
         <v>Norma</v>
       </c>
       <c r="M7" s="61" t="str">
@@ -7514,7 +7458,7 @@
         <v>1557</v>
       </c>
       <c r="W7" s="63" t="str">
-        <f t="shared" ref="W2:W20" si="7">CONCATENATE("Key.ABNT.",A7)</f>
+        <f t="shared" ref="W7:W20" si="7">CONCATENATE("Key.ABNT.",A7)</f>
         <v>Key.ABNT.7</v>
       </c>
       <c r="X7" s="43" t="s">
@@ -10625,32 +10569,22 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A7:A41">
-    <cfRule type="cellIs" dxfId="27" priority="10" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z20:Z41">
-    <cfRule type="duplicateValues" dxfId="22" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1 AA7:AA19">
-    <cfRule type="cellIs" dxfId="21" priority="14" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A6">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+  <conditionalFormatting sqref="A2:A41">
+    <cfRule type="cellIs" dxfId="21" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="Z20:Z41">
+    <cfRule type="duplicateValues" dxfId="16" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA1:AA19">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10803,7 +10737,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10849,7 +10783,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -71655,65 +71589,65 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="18" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:I2 N2:Q2 AB2:XFD2 P2:AA732 D3:E3 D4:D732">
-    <cfRule type="cellIs" dxfId="17" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1 F1">
-    <cfRule type="cellIs" dxfId="16" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="20" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="15" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="12" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="11" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="9" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_5I.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_5I.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C3E517-006A-44B6-ADE5-13E124407F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B7D09E-24CD-4F2F-953D-2180E46211F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19893" uniqueCount="1771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19893" uniqueCount="1770">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -5386,9 +5386,6 @@
   </si>
   <si>
     <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
-  </si>
-  <si>
-    <t>Arquitetura</t>
   </si>
   <si>
     <t>[ 5I ]</t>
@@ -5746,7 +5743,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5941,7 +5938,6 @@
     <xf numFmtId="0" fontId="6" fillId="31" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5956,63 +5952,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{8576210E-162F-453B-B886-CD2163C7562E}"/>
   </cellStyles>
-  <dxfs count="28">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="22">
     <dxf>
       <font>
         <b val="0"/>
@@ -6740,7 +6680,7 @@
       </c>
       <c r="B18" s="4">
         <f ca="1">NOW()</f>
-        <v>46216.265976736111</v>
+        <v>46219.565372569443</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>1541</v>
@@ -6845,9 +6785,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1A90C8D-F4F0-474F-8F2D-D62CBC6EB14C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA41"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" style="67" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" style="66" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.83203125" style="32" customWidth="1"/>
     <col min="3" max="3" width="6.5" style="32" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" style="32" customWidth="1"/>
@@ -6860,12 +6800,12 @@
     <col min="15" max="15" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="75.83203125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="59.1640625" customWidth="1"/>
-    <col min="18" max="18" width="6" style="66" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7" customWidth="1"/>
     <col min="20" max="20" width="9.1640625" customWidth="1"/>
     <col min="21" max="21" width="10" customWidth="1"/>
     <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.1640625" style="66" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="9" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="11" customWidth="1"/>
@@ -6939,7 +6879,7 @@
       <c r="V1" s="23" t="s">
         <v>1485</v>
       </c>
-      <c r="W1" s="68" t="s">
+      <c r="W1" s="67" t="s">
         <v>1504</v>
       </c>
       <c r="X1" s="39" t="s">
@@ -6955,7 +6895,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="32" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" s="32" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="56">
         <v>2</v>
       </c>
@@ -7027,9 +6967,9 @@
         <v>Contêineres</v>
       </c>
       <c r="V2" s="42" t="s">
-        <v>1765</v>
-      </c>
-      <c r="W2" s="69" t="str">
+        <v>1554</v>
+      </c>
+      <c r="W2" s="68" t="str">
         <f>CONCATENATE("Key-ABNT-",A2)</f>
         <v>Key-ABNT-2</v>
       </c>
@@ -7040,14 +6980,14 @@
         <v>33</v>
       </c>
       <c r="Z2" s="42" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="AA2" s="42" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" s="32" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" s="32" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="56">
         <v>3</v>
       </c>
@@ -7098,7 +7038,7 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="42" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="Q3" s="42" t="s">
         <v>1764</v>
@@ -7119,9 +7059,9 @@
         <v>Contêineres</v>
       </c>
       <c r="V3" s="42" t="s">
-        <v>1765</v>
-      </c>
-      <c r="W3" s="69" t="str">
+        <v>1554</v>
+      </c>
+      <c r="W3" s="68" t="str">
         <f t="shared" ref="W3:W41" si="4">CONCATENATE("Key-ABNT-",A3)</f>
         <v>Key-ABNT-3</v>
       </c>
@@ -7139,7 +7079,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="32" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" s="32" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="56">
         <v>4</v>
       </c>
@@ -7190,7 +7130,7 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="42" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="Q4" s="42" t="s">
         <v>1764</v>
@@ -7211,9 +7151,9 @@
         <v>Contêineres</v>
       </c>
       <c r="V4" s="42" t="s">
-        <v>1765</v>
-      </c>
-      <c r="W4" s="69" t="str">
+        <v>1554</v>
+      </c>
+      <c r="W4" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-4</v>
       </c>
@@ -7231,7 +7171,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" s="32" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" s="32" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="56">
         <v>5</v>
       </c>
@@ -7282,7 +7222,7 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="42" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="Q5" s="42" t="s">
         <v>1764</v>
@@ -7303,9 +7243,9 @@
         <v>Contêineres</v>
       </c>
       <c r="V5" s="42" t="s">
-        <v>1765</v>
-      </c>
-      <c r="W5" s="69" t="str">
+        <v>1554</v>
+      </c>
+      <c r="W5" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-5</v>
       </c>
@@ -7323,7 +7263,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" s="32" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" s="32" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="56">
         <v>6</v>
       </c>
@@ -7374,7 +7314,7 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="42" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="Q6" s="42" t="s">
         <v>1764</v>
@@ -7395,9 +7335,9 @@
         <v>Contêineres</v>
       </c>
       <c r="V6" s="42" t="s">
-        <v>1765</v>
-      </c>
-      <c r="W6" s="69" t="str">
+        <v>1554</v>
+      </c>
+      <c r="W6" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-6</v>
       </c>
@@ -7489,7 +7429,7 @@
       <c r="V7" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W7" s="69" t="str">
+      <c r="W7" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-7</v>
       </c>
@@ -7580,7 +7520,7 @@
       <c r="V8" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W8" s="69" t="str">
+      <c r="W8" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-8</v>
       </c>
@@ -7671,7 +7611,7 @@
       <c r="V9" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W9" s="69" t="str">
+      <c r="W9" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-9</v>
       </c>
@@ -7762,7 +7702,7 @@
       <c r="V10" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W10" s="69" t="str">
+      <c r="W10" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-10</v>
       </c>
@@ -7853,7 +7793,7 @@
       <c r="V11" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W11" s="69" t="str">
+      <c r="W11" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-11</v>
       </c>
@@ -7944,7 +7884,7 @@
       <c r="V12" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W12" s="69" t="str">
+      <c r="W12" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-12</v>
       </c>
@@ -8035,7 +7975,7 @@
       <c r="V13" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W13" s="69" t="str">
+      <c r="W13" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-13</v>
       </c>
@@ -8126,7 +8066,7 @@
       <c r="V14" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W14" s="69" t="str">
+      <c r="W14" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-14</v>
       </c>
@@ -8217,7 +8157,7 @@
       <c r="V15" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W15" s="69" t="str">
+      <c r="W15" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-15</v>
       </c>
@@ -8308,7 +8248,7 @@
       <c r="V16" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W16" s="69" t="str">
+      <c r="W16" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-16</v>
       </c>
@@ -8399,7 +8339,7 @@
       <c r="V17" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W17" s="69" t="str">
+      <c r="W17" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-17</v>
       </c>
@@ -8490,7 +8430,7 @@
       <c r="V18" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W18" s="69" t="str">
+      <c r="W18" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-18</v>
       </c>
@@ -8581,7 +8521,7 @@
       <c r="V19" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W19" s="69" t="str">
+      <c r="W19" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-19</v>
       </c>
@@ -8672,7 +8612,7 @@
       <c r="V20" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W20" s="69" t="str">
+      <c r="W20" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-20</v>
       </c>
@@ -8763,7 +8703,7 @@
       <c r="V21" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W21" s="69" t="str">
+      <c r="W21" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-21</v>
       </c>
@@ -8854,7 +8794,7 @@
       <c r="V22" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W22" s="69" t="str">
+      <c r="W22" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-22</v>
       </c>
@@ -8945,7 +8885,7 @@
       <c r="V23" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W23" s="69" t="str">
+      <c r="W23" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-23</v>
       </c>
@@ -9036,7 +8976,7 @@
       <c r="V24" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W24" s="69" t="str">
+      <c r="W24" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-24</v>
       </c>
@@ -9127,7 +9067,7 @@
       <c r="V25" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W25" s="69" t="str">
+      <c r="W25" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-25</v>
       </c>
@@ -9218,7 +9158,7 @@
       <c r="V26" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W26" s="69" t="str">
+      <c r="W26" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-26</v>
       </c>
@@ -9309,7 +9249,7 @@
       <c r="V27" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W27" s="69" t="str">
+      <c r="W27" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-27</v>
       </c>
@@ -9400,7 +9340,7 @@
       <c r="V28" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W28" s="69" t="str">
+      <c r="W28" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-28</v>
       </c>
@@ -9491,7 +9431,7 @@
       <c r="V29" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W29" s="69" t="str">
+      <c r="W29" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-29</v>
       </c>
@@ -9582,7 +9522,7 @@
       <c r="V30" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W30" s="69" t="str">
+      <c r="W30" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-30</v>
       </c>
@@ -9673,7 +9613,7 @@
       <c r="V31" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W31" s="69" t="str">
+      <c r="W31" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-31</v>
       </c>
@@ -9764,7 +9704,7 @@
       <c r="V32" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W32" s="69" t="str">
+      <c r="W32" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-32</v>
       </c>
@@ -9855,7 +9795,7 @@
       <c r="V33" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W33" s="69" t="str">
+      <c r="W33" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-33</v>
       </c>
@@ -9946,7 +9886,7 @@
       <c r="V34" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W34" s="69" t="str">
+      <c r="W34" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-34</v>
       </c>
@@ -10037,7 +9977,7 @@
       <c r="V35" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W35" s="69" t="str">
+      <c r="W35" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-35</v>
       </c>
@@ -10128,7 +10068,7 @@
       <c r="V36" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W36" s="69" t="str">
+      <c r="W36" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-36</v>
       </c>
@@ -10219,7 +10159,7 @@
       <c r="V37" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W37" s="69" t="str">
+      <c r="W37" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-37</v>
       </c>
@@ -10310,7 +10250,7 @@
       <c r="V38" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W38" s="69" t="str">
+      <c r="W38" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-38</v>
       </c>
@@ -10401,7 +10341,7 @@
       <c r="V39" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W39" s="69" t="str">
+      <c r="W39" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-39</v>
       </c>
@@ -10492,7 +10432,7 @@
       <c r="V40" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W40" s="69" t="str">
+      <c r="W40" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-40</v>
       </c>
@@ -10583,7 +10523,7 @@
       <c r="V41" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="W41" s="69" t="str">
+      <c r="W41" s="68" t="str">
         <f t="shared" si="4"/>
         <v>Key-ABNT-41</v>
       </c>
@@ -10601,32 +10541,22 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A7:A41">
-    <cfRule type="cellIs" dxfId="27" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z20:Z41">
-    <cfRule type="duplicateValues" dxfId="22" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1 AA7:AA19">
-    <cfRule type="cellIs" dxfId="21" priority="7" operator="equal">
+  <conditionalFormatting sqref="A2:B41">
+    <cfRule type="cellIs" dxfId="21" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B6 B7:B41">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+  <conditionalFormatting sqref="Z20:Z41">
+    <cfRule type="duplicateValues" dxfId="16" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+  <conditionalFormatting sqref="AA1:AA19">
+    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10779,7 +10709,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10825,7 +10755,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -71631,65 +71561,65 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="18" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:I2 N2:Q2 AB2:XFD2 P2:AA732 D3:E3 D4:D732">
-    <cfRule type="cellIs" dxfId="17" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1 F1">
-    <cfRule type="cellIs" dxfId="16" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="20" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="15" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="12" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="11" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="9" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_5I.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_5I.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8FCA05A-8D02-430A-B7BB-01FDF097992F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB440F5-69E3-4505-B249-068C73ED0881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19893" uniqueCount="1776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19932" uniqueCount="1802">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -5419,13 +5419,91 @@
   </si>
   <si>
     <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 5I. Building Information Codes.</t>
+  </si>
+  <si>
+    <t>Fonte1</t>
+  </si>
+  <si>
+    <t>https://brasil.un.org/pt-br/sdgs</t>
+  </si>
+  <si>
+    <t>Fonte2</t>
+  </si>
+  <si>
+    <t>https://eaesp.fgv.br/centros/centro-estudos-sustentabilidade/projetos/programa-brasileiro-ghg-protocol</t>
+  </si>
+  <si>
+    <t>Fonte3</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/acesso-a-informacao/acoes-e-programas/transformacao-ecologica/transformacao-ecologica</t>
+  </si>
+  <si>
+    <t>FonteVegetação1</t>
+  </si>
+  <si>
+    <t>https://museunacional.ufrj.br/hortobotanico</t>
+  </si>
+  <si>
+    <t>FonteVegetação2</t>
+  </si>
+  <si>
+    <t>https://www.embrapa.br/florestas/publicacoes</t>
+  </si>
+  <si>
+    <t>FonteVegetação3</t>
+  </si>
+  <si>
+    <t>https://www.arvoresgigantes.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação4</t>
+  </si>
+  <si>
+    <t>https://www.scielo.br/j/abb</t>
+  </si>
+  <si>
+    <t>FonteVegetação5</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/inpa/pt-br/Pesquisa/colecoes/botanica</t>
+  </si>
+  <si>
+    <t>FonteVegetação6</t>
+  </si>
+  <si>
+    <t>https://botanicasaopaulo.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação7</t>
+  </si>
+  <si>
+    <t>https://pesquisa.in.gov.br/imprensa</t>
+  </si>
+  <si>
+    <t>FonteVegetação8</t>
+  </si>
+  <si>
+    <t>https://mapas.florestal.gov.br</t>
+  </si>
+  <si>
+    <t>FonteTSB</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/orgaos/spe/taxonomia-sustentavel-brasileira/cadernos</t>
+  </si>
+  <si>
+    <t>FonteSINAPI</t>
+  </si>
+  <si>
+    <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <color theme="1"/>
@@ -5507,8 +5585,34 @@
       <name val="Arial Nova Cond Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color theme="10"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial Nova Cond"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="6"/>
+      <color theme="10"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="32">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5695,6 +5799,12 @@
         <bgColor rgb="FFFEF2CB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -5757,11 +5867,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5968,38 +6079,31 @@
     <xf numFmtId="0" fontId="3" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="16" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{8576210E-162F-453B-B886-CD2163C7562E}"/>
   </cellStyles>
-  <dxfs count="25">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="23">
     <dxf>
       <font>
         <b val="0"/>
@@ -6129,6 +6233,16 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -6524,7 +6638,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FFEA285-1F1C-49D4-8690-0B8CB6A5C474}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
@@ -6727,7 +6841,7 @@
       </c>
       <c r="B18" s="4">
         <f ca="1">NOW()</f>
-        <v>46232.782998379633</v>
+        <v>46233.477253356483</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>1540</v>
@@ -6823,7 +6937,157 @@
         <v>1542</v>
       </c>
     </row>
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B27" s="70" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C27" s="44" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>1778</v>
+      </c>
+      <c r="B28" s="71" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C28" s="44" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B29" s="71" t="s">
+        <v>1781</v>
+      </c>
+      <c r="C29" s="44" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="7" t="s">
+        <v>1782</v>
+      </c>
+      <c r="B30" s="72" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C30" s="44" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="7" t="s">
+        <v>1784</v>
+      </c>
+      <c r="B31" s="72" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C31" s="44" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="7" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B32" s="72" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C32" s="44" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B33" s="74" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C33" s="44" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="7" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B34" s="74" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C34" s="44" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="7" t="s">
+        <v>1792</v>
+      </c>
+      <c r="B35" s="72" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C35" s="44" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="7" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B36" s="74" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C36" s="44" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="73" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="7" t="s">
+        <v>1796</v>
+      </c>
+      <c r="B37" s="72" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C37" s="44" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B38" s="75" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C38" s="44" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="77" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="7" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B39" s="76" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C39" s="44" t="s">
+        <v>1540</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{067F4D6C-0B09-4C92-8A46-216A77CEE304}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{4000D332-CFDA-4B9C-A084-E7A14228DC56}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{8042119B-4FB2-46D2-96D1-316AE7C0D4C3}"/>
+    <hyperlink ref="B38" r:id="rId4" xr:uid="{C4EB7D50-046D-4ACE-8C9B-2171B8D0B3BC}"/>
+    <hyperlink ref="B39" r:id="rId5" location="categoria_888" xr:uid="{39422704-E979-44E7-9B3F-43165D2BF3A9}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -10588,35 +10852,25 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B6 A20:B41">
-    <cfRule type="cellIs" dxfId="24" priority="9" operator="equal">
+  <conditionalFormatting sqref="A2:B41">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="23" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F19">
+    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z20:Z41">
-    <cfRule type="duplicateValues" dxfId="19" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA6">
-    <cfRule type="cellIs" dxfId="18" priority="8" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7:B19">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F19">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA19">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+  <conditionalFormatting sqref="AA1:AA19">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10769,7 +11023,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10815,7 +11069,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -71621,65 +71875,65 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="15" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:I2 N2:Q2 AB2:XFD2 P2:AA732 D3:E3 D4:D732">
-    <cfRule type="cellIs" dxfId="14" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1 F1">
-    <cfRule type="cellIs" dxfId="13" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="20" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="12" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="11" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="9" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="8" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="6" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
